--- a/光伏配储项目/电价数据/2026/水口站.xlsx
+++ b/光伏配储项目/电价数据/2026/水口站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5174299999999999</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.9549800000000001</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.59911</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.7795599999999999</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.64302</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.61441</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43781</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45434</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44054</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42287</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42886</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40845</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39754</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39923</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38392</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40174</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42293</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.4116</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35353</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38447</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39254</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42196</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41296</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42296</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41253</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44398</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.38954</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30394</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.2624</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.30237</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.32591</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.51105</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.44825</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.26544</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.17646</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.23822</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.28046</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.3065</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.1049</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.20327</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.4149</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.40965</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.19892</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.01447</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.25777</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.09448000000000001</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.19221</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.24723</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.27228</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.25088</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.4795</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.35446</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.0799</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.30927</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.17486</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.40406</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.41723</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.50166</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.447</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.42686</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.5967100000000001</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.08704</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.17297</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.13465</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.6004700000000001</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.8978200000000001</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.6575299999999999</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.54413</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.63328</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.76593</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.69494</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.99839</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.14283</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.85246</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.24498</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.64374</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.9308</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.7803600000000001</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.61873</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.90501</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.82456</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.8640099999999999</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.83708</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.58102</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47943</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40185</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41307</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42232</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.8691599999999999</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.8437</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.88201</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53607</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5224800000000001</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5062300000000001</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.53737</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49798</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.41197</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47258</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38937</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38088</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39201</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37074</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35597</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37549</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37545</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38044</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42121</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.52137</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.65762</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.72414</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.44151</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.38383</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.4484</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.3459100000000001</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.60019</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.6075900000000001</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.72315</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.60221</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.59516</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.60117</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.60345</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.60425</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.39686</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.46979</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.6892</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.72504</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.01369</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.37989</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.64816</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.71528</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.5909800000000001</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.6254999999999999</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.98665</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.73766</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.50356</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.61764</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.29488</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.60229</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.60942</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.6090399999999999</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.60784</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.81635</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.60387</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.51976</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.5769299999999999</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.57847</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.40681</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.42895</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.70548</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.58429</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.52658</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.7447999999999999</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.53467</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.00872</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.1743</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.0923</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.92698</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.0248</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.00833</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.17657</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.84261</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.91772</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.17084</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.5891900000000001</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.38211</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.51028</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.50282</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.6630499999999999</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44076</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43477</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41815</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37745</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>1.18718</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>1.18422</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>1.18716</v>
+      </c>
+      <c r="C119" t="n">
+        <v>1.18892</v>
+      </c>
+      <c r="D119" t="n">
+        <v>1.18573</v>
+      </c>
+      <c r="E119" t="n">
+        <v>1.19122</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1.19143</v>
+      </c>
+      <c r="G119" t="n">
+        <v>1.1874</v>
+      </c>
+      <c r="H119" t="n">
+        <v>1.18729</v>
+      </c>
+      <c r="I119" t="n">
+        <v>1.1876</v>
+      </c>
+      <c r="J119" t="n">
+        <v>1.18652</v>
+      </c>
+      <c r="K119" t="n">
+        <v>1.17804</v>
+      </c>
+      <c r="L119" t="n">
+        <v>1.17812</v>
+      </c>
+      <c r="M119" t="n">
+        <v>1.18713</v>
+      </c>
+      <c r="N119" t="n">
+        <v>1.18694</v>
+      </c>
+      <c r="O119" t="n">
+        <v>1.18326</v>
+      </c>
+      <c r="P119" t="n">
+        <v>1.18642</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>1.18687</v>
+      </c>
+      <c r="R119" t="n">
+        <v>1.17832</v>
+      </c>
+      <c r="S119" t="n">
+        <v>1.18717</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35859</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36308</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>1.18665</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>1.18711</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>1.18697</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>1.18536</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>1.18404</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>1.18512</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>1.18463</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>1.18209</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.48448</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.41715</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.45494</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.40652</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.37107</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.46014</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30876</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31215</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.30276</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.35283</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.5758</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.5728799999999999</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.80743</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.44966</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.67718</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.7793</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.43738</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.42884</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.48634</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.5219400000000001</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.58815</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.5624</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.42041</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.33668</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.57777</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.58114</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.6056699999999999</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.79726</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.20228</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.68189</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.81041</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.22054</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.62259</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.5726599999999999</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.49327</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.61353</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.8878400000000001</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.8645900000000001</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.79838</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.55964</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.78351</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.70768</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.96821</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.6381100000000001</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.90674</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.63106</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.6519299999999999</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.83638</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.65901</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.59284</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.68362</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.6123500000000001</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.60005</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.60004</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.5962000000000001</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.6000599999999999</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.60011</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.60011</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.6088</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.59572</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.59639</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.5971000000000001</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.59963</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.59957</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.5996</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.99618</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.59626</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.59948</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.5989099999999999</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.6381699999999999</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.59888</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.59919</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.59902</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.59923</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.5992799999999999</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.59976</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.5997100000000001</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.5996699999999999</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.59993</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.5997400000000001</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.5993099999999999</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.60019</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.59799</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.59909</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.59937</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.59848</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.59911</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.59965</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.59992</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.60042</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.60033</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.37973</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.52252</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.49893</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.39166</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.43903</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.5241399999999999</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.45316</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.80022</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.7236399999999999</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.5069900000000001</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.63074</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.5723200000000001</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.40827</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.29696</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.2746499999999999</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.39399</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.34327</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.33208</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.49094</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.70605</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.30279</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.37406</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.48792</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.46682</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.47288</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.43683</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.45413</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.59384</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.33199</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.74758</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.44053</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.8986900000000001</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.4323</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.3642</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.43654</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.47862</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.44272</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.48684</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.5620299999999999</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.60677</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.57725</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.83748</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.56264</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.53532</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.47057</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.4831</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.49819</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.5027200000000001</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.47327</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.46307</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.39548</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.33447</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31637</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.39982</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.30131</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.85539</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.81862</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.7576900000000001</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.7500800000000001</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.6002000000000001</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.6002999999999999</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.6028600000000001</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.6048</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.60246</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.60215</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.60025</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.60034</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.61097</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.6006900000000001</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.60019</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.5998600000000001</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.60001</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.5998</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.5998600000000001</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.59984</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29467</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.60024</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.60025</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.60021</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.2961</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.60023</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.6002000000000001</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.59989</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.59958</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>1.32443</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.5945199999999999</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.5992999999999999</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.5993099999999999</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.6002799999999999</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.6003200000000001</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.60405</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.60073</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.60441</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.6053099999999999</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.60081</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.09888</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.08996999999999999</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.60141</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.61149</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.6020800000000001</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.60158</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.07052</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.09053</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.05553</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.06853000000000001</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.01387</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.07282</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.01251</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.08807</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.06769</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.01307</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.04588</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.04493</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.04148</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.05048</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.0296</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21012</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.08984</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.09079999999999999</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.00583</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.01102</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.05094</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.0095</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.21424</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.11604</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.6023099999999999</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.60015</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.59484</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.32917</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.36178</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.37849</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.40227</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39312</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.40274</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37511</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35249</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>1.39955</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>1.39844</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>1.40988</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>1.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35836</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>1.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>1.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>1.46141</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>1.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.37674</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.7637</v>
+      </c>
+      <c r="D122" t="n">
+        <v>1.49895</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1.54026</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.45245</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.44793</v>
+      </c>
+      <c r="H122" t="n">
+        <v>1.3664</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.36862</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.36515</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.31603</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.36443</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35698</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.35173</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.3464</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31906</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33167</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32489</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30584</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32489</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.13472</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04885</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.01086</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04481</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04318</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04176</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.02901</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.13083</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.01218</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.0434</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.00137</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.0156</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04294</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04286</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04494</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04482999999999999</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.03541</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.0423</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04461</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04216</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04232</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.0109</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04452</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04255</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.01215</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.01059</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.04992</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.01225</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.01081</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.01241</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.01475</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.01526</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.22994</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.18885</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.30866</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.30728</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.31157</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.31139</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.31025</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.31294</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.28689</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.32103</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.31277</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.35751</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.3362</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.33752</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31301</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.4055299999999999</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30487</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28751</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29864</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.29301</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28709</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27813</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27708</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28611</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.19438</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.18244</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17179</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16014</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15938</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23743</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21479</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.23931</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27516</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.29015</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29521</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.2874</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28766</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27853</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28818</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31454</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.31166</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.39229</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.45764</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.38414</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.43796</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.45088</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.52313</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45682</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33728</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.42732</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.47197</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.45438</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.49214</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.3569</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15297</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29392</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31239</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31212</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.41283</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.38166</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.38923</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.42588</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47944</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.54947</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7925</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6524500000000001</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.43795</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.54411</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.82626</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.01233</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.56052</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.01748</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.98163</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.40438</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.45146</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.99561</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.71139</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.31779</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.97526</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.86456</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.42795</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.12094</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.59176</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.8053400000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5303600000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7877000000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78899</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87858</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8814099999999999</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.50664</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.4121</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41725</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.46536</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.22435</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87937</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.63939</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54262</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50257</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45789</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42624</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.4401600000000001</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45068</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39254</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45284</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42073</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36529</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38929</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39062</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.34842</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35342</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40655</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35538</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.4509</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>1.39769</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>1.40012</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>1.58944</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.4294</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>1.59623</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.5970599999999999</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>1.66145</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>1.55357</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>1.45423</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5671900000000001</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.47326</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.97836</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.69952</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.92976</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.91099</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.91871</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.37312</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.49118</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.36799</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.38247</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.44054</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>1.50544</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>1.36696</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.35559</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.47703</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>1.42309</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>1.59773</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.38994</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.39363</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.36224</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.36927</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.37674</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>1.39971</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>1.36588</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.3725</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.38022</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.36124</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.37093</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.36945</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.35391</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.36753</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.37568</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.39519</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.37332</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.40248</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.38279</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.38255</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.40701</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.39163</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.38747</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.38284</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.37941</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.36649</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.34639</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.42527</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41257</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45231</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41493</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39145</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.3749</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35327</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9561499999999999</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.47691</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.40762</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.48199</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.5445800000000001</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.39252</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40968</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.39169</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.41424</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.38351</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38568</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40008</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.40053</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.36055</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.36462</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.37318</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.41197</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.44433</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.39314</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.23386</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.42795</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.40684</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.44345</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.40688</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.37748</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.3931</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.40464</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.23003</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.34444</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.29586</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.32365</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.42064</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.55367</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.45327</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.38754</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.47777</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.40754</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.40035</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.37018</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.52485</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.30926</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.33617</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.2998</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.35306</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.26972</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32302</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.30745</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.29487</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.2804700000000001</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.34719</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.23042</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.29658</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.36119</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>-0.01271</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43249</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.36109</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.29408</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.3236</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42044</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59675</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.9388300000000001</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.44767</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.20046</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7036</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79535</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64979</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58365</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5005500000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.5658099999999999</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.42535</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.6924400000000001</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.5066700000000001</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.46086</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.36906</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.53801</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.37555</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.54312</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.85384</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.7034400000000001</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.59842</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.44866</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.31661</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.76287</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.75976</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.46248</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.44238</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.65395</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.6891</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.5050899999999999</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.28906</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.32331</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.39846</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.47941</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.47104</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.42933</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.42291</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.41844</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.42189</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.47942</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.4638</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.43836</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.48397</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.5958300000000001</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.50588</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.46849</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.50152</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.45205</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.45485</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.57286</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.49808</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.47384</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.5131</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.46139</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.44903</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.7816900000000001</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.57925</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.9344</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.67164</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.5358200000000001</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.49215</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.48214</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.3865</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36957</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33453</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32473</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42548</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33943</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32617</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32493</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32413</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32617</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.3102200000000001</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32513</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31121</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39151</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35489</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.30376</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.30936</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.33282</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.00735</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.3157</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.26698</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.1849</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.18988</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31484</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.20144</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.5904700000000001</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.596</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.17385</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.18072</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.19687</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.19368</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.29799</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.20346</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.3092200000000001</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.31159</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.19055</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.18105</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.17354</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.17685</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.20499</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.20012</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.18578</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34161</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.40855</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.3751</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36157</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.40538</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44972</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39981</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40188</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44362</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43992</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4392799999999999</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.4442</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40266</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39054</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34934</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5424</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38908</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46869</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42386</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41593</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37014</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39307</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36988</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38024</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39108</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37024</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38026</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35517</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37019</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38011</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34024</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34452</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35155</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37551</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28937</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31352</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28653</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28604</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.30803</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26188</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.26972</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.25782</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.22808</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.2476</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.2984</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.29127</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31411</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.29284</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.33841</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.30473</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28818</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.26999</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31539</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30186</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.31503</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.3761</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.46554</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.43325</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.4285</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.49739</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.6319600000000001</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.60258</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.50617</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.38431</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.36365</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.3836</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.47745</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.54764</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.62429</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.62352</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.49608</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.41728</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.40051</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.37975</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.37032</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.36307</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41951</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.39223</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.39831</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.39609</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.38563</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.38387</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36025</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41861</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.45562</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38047</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35276</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34917</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34137</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.3429</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34184</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.36296</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.40105</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.34826</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.48594</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.35873</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.57521</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.58045</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.56916</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.57164</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.7920199999999999</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.7801900000000001</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.52155</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.62944</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.91677</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.55636</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.90097</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.7809700000000001</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.7737000000000001</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.84108</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.26082</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.6263200000000001</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27902</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.9247000000000001</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.60199</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.60841</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.5624199999999999</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.77328</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.7563799999999999</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.78975</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.8030900000000001</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.79822</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.77539</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.79984</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.6478400000000001</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.83301</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.96984</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.91431</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.90197</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.8299</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.83763</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.8457100000000001</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.79103</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.87999</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.56412</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.60645</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.82372</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.83208</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.82601</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.18452</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.90538</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.22203</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.8556</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.96025</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.5193099999999999</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.45508</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.38252</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.61933</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.32381</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.86575</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.5904700000000001</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34232</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.38761</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.32417</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.33461</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.31437</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.31721</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.40173</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.60712</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.34134</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.33222</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.33505</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32541</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32647</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34592</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33872</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32661</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.33224</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.62562</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.6301</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.36306</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.48035</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.38169</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.39421</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.39266</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29026</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34172</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29875</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28194</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.32634</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33602</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32267</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32917</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32602</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.34884</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.38777</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.5360499999999999</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.7268</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.63878</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.54548</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.48264</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.35438</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.39608</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.38957</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.39292</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.38547</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.41896</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.3676</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36146</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36776</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37307</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36202</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39283</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40286</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.3694</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34931</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35972</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36928</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.36428</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33669</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.36186</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.29357</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.33304</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.3258</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32963</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.33064</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.36845</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.47913</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35759</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.39554</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.83273</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.39083</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.35306</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.3662</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33903</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.38232</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.56229</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38909</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.38149</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.39959</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.37543</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.48782</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.40612</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.40775</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38363</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.4297</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40916</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38571</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38502</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65195</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.8308099999999999</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47175</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45942</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35957</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34477</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.3127200000000001</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41074</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37579</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36129</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35916</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36233</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36056</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35678</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35814</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.35171</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.35827</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.29023</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.21041</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.39996</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.29559</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.29443</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.22629</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.34366</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.28862</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.29051</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.01943</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.24769</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.2985</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.22113</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.03694</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.19126</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.06439</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.28279</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.32656</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.31731</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.46214</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.5237</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.5679</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1.42817</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.5305800000000001</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1.01439</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.49626</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.9936200000000001</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.45483</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.40474</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.74169</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>1.52427</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.59788</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>1.04848</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.65942</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>1.51993</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>1.06107</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.9510599999999999</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.5676</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.61795</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.61926</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43004</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41895</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37805</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37448</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36015</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34534</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.54748</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.7619199999999999</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.6712899999999999</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.94232</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41942</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.4053</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40493</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41136</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.4090299999999999</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41774</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40006</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39587</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41164</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40938</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39366</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38712</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41849</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38727</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41663</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39008</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.3999</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39986</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41249</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.3999</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45051</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44948</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56059</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.5006499999999999</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45069</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.41971</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.8007000000000001</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.81609</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.16017</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.22682</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.34004</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.44869</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.38004</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.24414</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.7104400000000001</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.73388</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.82933</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.56945</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.5596100000000001</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.57421</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.37624</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>-0.02414</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>-0.03261</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.23178</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.30093</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.04762</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.79543</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.55215</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.12292</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.6112799999999999</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.55083</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.46364</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.6223500000000001</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.46949</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.5919099999999999</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.36954</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37237</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.41501</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.40529</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.47135</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.55589</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.45293</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.52661</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.54103</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.58229</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.7538400000000001</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.7025800000000001</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.65024</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.65137</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.63928</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.76977</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.02497</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.5013</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.15105</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.07011</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.8175399999999999</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.37338</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.85061</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7861900000000001</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6374099999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.04361</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.65637</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.73698</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.59963</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47839</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.47173</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41939</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.55065</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.39878</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.39874</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45812</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.4367799999999999</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42654</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44835</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41782</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40082</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45769</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39933</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40704</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39862</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38853</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37486</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.3767799999999999</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38657</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37958</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36647</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.40994</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.40411</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.39134</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.43973</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39446</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38659</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.38344</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.43705</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.42628</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.44056</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.47313</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.59287</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.71593</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.30568</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.11528</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.16186</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.17257</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.37576</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.32771</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.02095</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30971</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31319</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.36752</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.40826</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.40477</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.41886</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.43651</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.42143</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36372</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41311</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41712</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.44908</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.42998</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.45514</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38086</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38628</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40611</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40201</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34409</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36549</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37798</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39921</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37946</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39963</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38081</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39388</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37906</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36415</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.51012</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.52093</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.46298</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.43091</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.38833</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37714</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37705</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.37377</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35628</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35517</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35122</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35747</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35076</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.35207</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34037</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34046</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33048</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33737</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.32097</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31675</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32448</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.25547</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.30558</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.27268</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.24966</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.26615</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.04364</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.19603</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29639</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29763</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.07635</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.18288</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04336</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.2787</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.03326</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.18077</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.19154</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.06636</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31174</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.0243</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.24215</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.24996</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.17493</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23422</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27951</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.31847</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.27092</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.31469</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30497</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.36322</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34663</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.37051</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.42469</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.39342</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35742</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.41288</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.39774</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.36901</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.41446</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.37046</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.42565</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39598</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.38875</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.39291</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.36919</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.38525</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.41503</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34789</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36513</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36983</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36591</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.3517</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.41438</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33841</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.35589</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.34717</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31028</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31061</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31088</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31659</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30682</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30682</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30931</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30615</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30682</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30741</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29688</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.26043</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.25426</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.17004</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.20942</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.45505</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.09423999999999999</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.08022</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.03987</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.0277</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.19195</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.03944</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.03903</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.02564</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.11368</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.19555</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.12386</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.05266</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.04086</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.03851</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.11211</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.02379</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.03093</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.02635</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.02394</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.03351</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.09670999999999999</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.06254999999999999</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.02356</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.02645</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.02358</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.02285</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.03603</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.02687</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.06357</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.04339</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.17333</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.20926</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.25409</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.2757</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.28031</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.27277</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.27786</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.29066</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.29846</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28631</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.3127200000000001</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30352</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.30516</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29469</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.30679</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.29404</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30881</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.29876</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.4612</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.31758</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.30622</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.2823</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.28998</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.27789</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.26896</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.23057</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.13815</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.54626</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.2909</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.17304</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.2837</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.32194</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.26285</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.29336</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.28092</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.26206</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.24487</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.23283</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.24998</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.25609</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.22167</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.25834</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.24837</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.26214</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.27093</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.27188</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.24954</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.28898</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.26495</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.30486</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.41104</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.30575</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.27636</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.22699</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.15322</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.6257699999999999</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.62873</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.73911</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.5857</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.48368</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.16674</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.27384</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.15463</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.12795</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>1.12393</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.1631</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.2819700000000001</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.15196</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.3152</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.12083</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.008880000000000001</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.1317</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.18838</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.05992</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.20292</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.03816</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.14498</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.29844</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.24368</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.09383</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.18791</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.32878</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.5206499999999999</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.17733</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.40635</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.39466</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.52949</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.48226</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.4986</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.4993</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.49889</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.54249</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.42019</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.51951</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.43514</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.54257</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.95589</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.69777</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.68288</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.72268</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.8476900000000001</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.6982200000000001</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.72785</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.74122</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.84558</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.56287</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.5128400000000001</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.55392</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.5529500000000001</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.6671699999999999</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.57333</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.48163</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.34649</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.41868</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32922</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.39798</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.45977</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.42529</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.42533</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.34221</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.1442</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.33845</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33509</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.33977</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.34878</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.96576</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.76423</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.66737</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.6161799999999999</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.49596</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.58477</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.50193</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.43969</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.108</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.54404</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.63454</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.7128</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.70741</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.55521</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.5729299999999999</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.45426</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.36644</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.36565</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.41567</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.16363</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.3683999999999999</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.28631</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.35563</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.36668</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.22843</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.39095</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.5828</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.33616</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.17059</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.35042</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.37054</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.37742</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.3915</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.39653</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.38849</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.39515</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.37245</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.35432</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.38866</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.40629</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.39708</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.43183</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.55608</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.5498999999999999</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.43301</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.77161</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.49686</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.49142</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.56359</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.53273</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.41144</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.41331</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.40182</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.38325</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.39017</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.34582</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.33015</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33358</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33356</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.36523</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.30974</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.34071</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.34926</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.33616</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.3444</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34788</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31224</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34343</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.34516</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32983</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35559</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36911</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35675</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.3733399999999999</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35941</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.43025</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.55661</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.3469100000000001</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.43789</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.54971</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.78263</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.7113400000000001</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.93755</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.03795</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.39561</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.507</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.5436299999999999</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.48962</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.46313</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.49692</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.47583</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.46446</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.34059</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.46764</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.32353</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.6393099999999999</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.3582</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.45891</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.48677</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.48651</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.14222</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.46835</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.41736</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.47873</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.50284</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.49713</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.54301</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.65479</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.67737</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.72424</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.79076</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.7739400000000001</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.84397</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.8564299999999999</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.83416</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.70812</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.61154</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.5945499999999999</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.4717</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.71578</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.5481699999999999</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.62185</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.54673</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.57641</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.5527000000000001</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.5184</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.53925</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42414</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.68324</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.50357</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40146</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45844</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.46224</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38015</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.50615</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.47774</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36265</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36867</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.56487</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40121</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40125</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39192</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37554</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37441</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37729</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36915</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36691</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36152</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37102</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39958</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37575</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.37703</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.39435</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.47162</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.61036</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.6020800000000001</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.5905</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.65852</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.6674099999999999</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.5718799999999999</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.74739</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.81835</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.52728</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.34414</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.52746</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.45425</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.53562</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.51836</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.51847</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.2419</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.23581</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.25453</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.49544</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.45562</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.34226</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.43391</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.20328</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.48221</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.5584</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.54262</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.6288400000000001</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.63117</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.42503</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.65211</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.42862</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.41024</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.44217</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.75744</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.6818500000000001</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.6169600000000001</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.5976699999999999</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.47113</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.54465</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5016</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.5021</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.46405</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.55475</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.53742</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.26207</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.68449</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.54249</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.4715299999999999</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.44968</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.72657</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.49334</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.49511</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39828</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.50543</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.48328</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.44752</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.38347</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36944</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37505</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27075</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.37128</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33226</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34983</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.41387</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34089</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.36359</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.34282</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.3414700000000001</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.34224</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.32172</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.33255</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.31945</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31695</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31868</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.30961</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.30687</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.38735</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.30534</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30037</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.29614</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.28958</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.36615</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.41572</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.34545</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.37188</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.59058</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.49958</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.78852</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.27612</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.20455</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.16518</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.78188</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.68572</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.20997</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.09938</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.00146</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.11489</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.10355</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.25089</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.01418</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.22763</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.09764</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.23241</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.21805</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.14684</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.3236</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.25282</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.52397</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.51691</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.3968</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.37542</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.4655</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.5404800000000001</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.592</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.4674</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.48046</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.39421</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.46194</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.47255</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.14858</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.005030000000000001</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.26217</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.28119</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.40426</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.30951</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.42953</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.5116000000000001</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.5177</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.54772</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.53335</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.51513</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.6417</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.4857</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.50375</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.45422</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.43994</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.38663</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.3782</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.3752799999999999</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.01363</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.52519</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.57874</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.6336799999999999</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.47969</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.36265</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.3888</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38514</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.35543</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.35632</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37863</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36592</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38019</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.35615</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36295</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36399</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36365</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38345</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.42147</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33611</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.31569</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.31552</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.39167</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.42991</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.41642</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.39692</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.42563</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.38887</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.43115</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.58299</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.36723</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.35961</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.26852</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.46549</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.29507</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.09861</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.08173999999999999</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.14341</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.09567000000000001</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.19125</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.53151</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.23933</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.33026</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.30656</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.40935</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.20647</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.29115</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>1.14122</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.89823</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.37159</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.85315</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.44356</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.78383</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>1.15908</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.24938</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.01831</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.84888</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.5864</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.51289</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.8199500000000001</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.8318300000000001</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.54935</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.81424</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.56751</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.6023500000000001</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.5922799999999999</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.58004</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.82968</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.65667</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.6612</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.6741200000000001</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.80667</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.5455099999999999</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.5688300000000001</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.5199199999999999</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.58969</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.73175</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.7950199999999999</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.57225</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.44023</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.41523</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.40796</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33527</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.6823400000000001</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.44694</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.44981</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.34428</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.38662</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.38414</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.37121</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41964</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.36613</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39146</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37332</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.35535</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32486</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32872</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34274</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.36412</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34777</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34636</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33403</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.31934</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.2835</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.26145</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.24389</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.1746</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.22807</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.31905</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.27827</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.26881</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.38881</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.32273</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.25439</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.2007</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.24494</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.23981</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22086</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.15178</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.16141</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.21567</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.15832</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.20407</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.16734</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.27717</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.23512</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.18885</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.12587</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20706</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.23276</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.28517</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.21983</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.50137</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.36436</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.40081</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.36904</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.38947</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.3924</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.39574</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.4094</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.45713</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.4798</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.42763</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.44283</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.34819</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.34736</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.5262</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.34325</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.4697</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.45808</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.43208</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.44026</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.5464199999999999</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.5647300000000001</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.51677</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.44788</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.45183</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.42534</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.40673</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.4085</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40968</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38407</v>
       </c>
     </row>
   </sheetData>
